--- a/SLA Report Overview.xlsx
+++ b/SLA Report Overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\IS\Quality Assurance\ACCESSIBILITY\SLA Monthly Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77EF209-72BA-4188-93E9-360210677828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFE7BF3-37E5-4F7C-9F31-0A3610E5BC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{C020AC1A-066C-49E3-9B8D-19805A06CB89}"/>
   </bookViews>
@@ -35,6 +35,7 @@
     <externalReference r:id="rId18"/>
     <externalReference r:id="rId19"/>
     <externalReference r:id="rId20"/>
+    <externalReference r:id="rId21"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -958,10 +959,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -1015,16 +1016,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$B$3:$B$20</c:f>
+              <c:f>'SLA and Time Data'!$B$3:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1078,6 +1082,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.35714285714285715</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.66666666666666663</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1396,10 +1403,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -1453,16 +1460,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$K$3:$K$20</c:f>
+              <c:f>'SLA and Time Data'!$K$3:$K$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="10" formatCode="0.0%">
                   <c:v>0.16666666666666666</c:v>
                 </c:pt>
@@ -1486,6 +1496,9 @@
                 </c:pt>
                 <c:pt idx="17" formatCode="0.0%">
                   <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="0.0%">
+                  <c:v>0.76923076923076927</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1799,10 +1812,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -1856,16 +1869,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$L$3:$L$20</c:f>
+              <c:f>'SLA and Time Data'!$L$3:$L$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="10" formatCode="0">
                   <c:v>183.5</c:v>
                 </c:pt>
@@ -1888,7 +1904,10 @@
                   <c:v>165</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0">
-                  <c:v>86.166666666666671</c:v>
+                  <c:v>117.16666666666667</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="0">
+                  <c:v>142.76923076923077</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2201,10 +2220,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -2258,16 +2277,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$M$3:$M$20</c:f>
+              <c:f>'SLA and Time Data'!$M$3:$M$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="10" formatCode="0">
                   <c:v>35.583333333333336</c:v>
                 </c:pt>
@@ -2291,6 +2313,9 @@
                 </c:pt>
                 <c:pt idx="17" formatCode="0">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="0">
+                  <c:v>0.23076923076923078</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2602,10 +2627,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -2659,16 +2684,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$C$3:$C$20</c:f>
+              <c:f>'SLA and Time Data'!$C$3:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>81.333333333333329</c:v>
                 </c:pt>
@@ -2722,6 +2750,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>162.28571428571428</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3034,10 +3065,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -3091,16 +3122,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$D$3:$D$20</c:f>
+              <c:f>'SLA and Time Data'!$D$3:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>-1.1666666666666667</c:v>
                 </c:pt>
@@ -3154,6 +3188,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2.7142857142857144</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3478,10 +3515,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -3535,16 +3572,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$E$3:$E$20</c:f>
+              <c:f>'SLA and Time Data'!$E$3:$E$21</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.75</c:v>
                 </c:pt>
@@ -3589,6 +3629,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.7142857142857143</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3902,10 +3945,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -3959,16 +4002,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$F$3:$F$20</c:f>
+              <c:f>'SLA and Time Data'!$F$3:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>19.5</c:v>
                 </c:pt>
@@ -4013,6 +4059,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>83.428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4325,10 +4374,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -4382,16 +4431,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$G$3:$G$20</c:f>
+              <c:f>'SLA and Time Data'!$G$3:$G$21</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.25</c:v>
                 </c:pt>
@@ -4436,6 +4488,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>-0.14285714285714285</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4752,10 +4807,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -4809,16 +4864,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$H$3:$H$20</c:f>
+              <c:f>'SLA and Time Data'!$H$3:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0.26666666666666666</c:v>
                 </c:pt>
@@ -4871,7 +4929,10 @@
                   <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.41666666666666669</c:v>
+                  <c:v>0.55555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5185,10 +5246,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -5242,16 +5303,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$I$3:$I$20</c:f>
+              <c:f>'SLA and Time Data'!$I$3:$I$21</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>336.33333333333331</c:v>
                 </c:pt>
@@ -5304,7 +5368,10 @@
                   <c:v>162.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>160.08333333333334</c:v>
+                  <c:v>160.55555555555554</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>326.28571428571428</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5617,10 +5684,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$A$3:$A$20</c:f>
+              <c:f>'SLA and Time Data'!$A$3:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>mmm\-yy</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>45412</c:v>
                 </c:pt>
@@ -5674,16 +5741,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45961</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SLA and Time Data'!$J$3:$J$20</c:f>
+              <c:f>'SLA and Time Data'!$J$3:$J$21</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>26.266666666666666</c:v>
                 </c:pt>
@@ -5736,7 +5806,10 @@
                   <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.5833333333333335</c:v>
+                  <c:v>1.5555555555555556</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-2.2857142857142856</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13188,6 +13261,9 @@
 <file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overview"/>
       <sheetName val="Prototypes"/>
@@ -13224,7 +13300,7 @@
         </row>
         <row r="21">
           <cell r="C21">
-            <v>2.5833333333333335</v>
+            <v>1.5555555555555556</v>
           </cell>
           <cell r="F21">
             <v>1</v>
@@ -13232,7 +13308,7 @@
         </row>
         <row r="24">
           <cell r="C24">
-            <v>0.41666666666666669</v>
+            <v>0.55555555555555558</v>
           </cell>
           <cell r="F24">
             <v>0.83333333333333337</v>
@@ -13240,10 +13316,82 @@
         </row>
         <row r="25">
           <cell r="C25">
-            <v>160.08333333333334</v>
+            <v>160.55555555555554</v>
           </cell>
           <cell r="F25">
-            <v>86.166666666666671</v>
+            <v>117.16666666666667</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Prototypes"/>
+      <sheetName val="50% Reviews"/>
+      <sheetName val="PSIAs"/>
+      <sheetName val="Peer Verifications"/>
+      <sheetName val="Holidays"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="10">
+          <cell r="C10">
+            <v>-0.5</v>
+          </cell>
+          <cell r="F10">
+            <v>-3.5</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>0.66666666666666663</v>
+          </cell>
+          <cell r="F13">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>126</v>
+          </cell>
+          <cell r="F14">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>-2.2857142857142856</v>
+          </cell>
+          <cell r="F21">
+            <v>0.23076923076923078</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>1</v>
+          </cell>
+          <cell r="F24">
+            <v>0.76923076923076927</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>326.28571428571428</v>
+          </cell>
+          <cell r="F25">
+            <v>142.76923076923077</v>
           </cell>
         </row>
       </sheetData>
@@ -13820,8 +13968,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C9A2F292-8058-4BAE-B08E-ED62D0005CC0}" name="SLAs_Over_Time" displayName="SLAs_Over_Time" ref="A2:M21" totalsRowCount="1" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
-  <autoFilter ref="A2:M20" xr:uid="{C9A2F292-8058-4BAE-B08E-ED62D0005CC0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C9A2F292-8058-4BAE-B08E-ED62D0005CC0}" name="SLAs_Over_Time" displayName="SLAs_Over_Time" ref="A2:M22" totalsRowCount="1" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
+  <autoFilter ref="A2:M21" xr:uid="{C9A2F292-8058-4BAE-B08E-ED62D0005CC0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M19">
     <sortCondition ref="A2:A19"/>
   </sortState>
@@ -14194,7 +14342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBD338C-EF25-4406-A530-FCF51186A088}">
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="9" customWidth="1"/>
@@ -15091,15 +15239,15 @@
       </c>
       <c r="H20" s="16">
         <f>[18]Overview!$C$24</f>
-        <v>0.41666666666666669</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I20" s="14">
         <f>[18]Overview!$C$25</f>
-        <v>160.08333333333334</v>
+        <v>160.55555555555554</v>
       </c>
       <c r="J20" s="14">
         <f>[18]Overview!$C$21</f>
-        <v>2.5833333333333335</v>
+        <v>1.5555555555555556</v>
       </c>
       <c r="K20" s="13">
         <f>[18]Overview!$F$24</f>
@@ -15107,123 +15255,171 @@
       </c>
       <c r="L20" s="14">
         <f>[18]Overview!$F$25</f>
-        <v>86.166666666666671</v>
+        <v>117.16666666666667</v>
       </c>
       <c r="M20" s="15">
         <f>[18]Overview!$F$21</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="19">
+        <v>45961</v>
+      </c>
+      <c r="B21" s="16">
+        <f>[19]Overview!$C$13</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C21" s="14">
+        <f>[19]Overview!$C$14</f>
+        <v>126</v>
+      </c>
+      <c r="D21" s="14">
+        <f>[19]Overview!$C$10</f>
+        <v>-0.5</v>
+      </c>
+      <c r="E21" s="13">
+        <f>[19]Overview!$F$13</f>
         <v>1</v>
       </c>
-      <c r="B21" s="26">
+      <c r="F21" s="14">
+        <f>[19]Overview!$F$14</f>
+        <v>32</v>
+      </c>
+      <c r="G21" s="15">
+        <f>[19]Overview!$F$10</f>
+        <v>-3.5</v>
+      </c>
+      <c r="H21" s="16">
+        <f>[19]Overview!$C$24</f>
+        <v>1</v>
+      </c>
+      <c r="I21" s="14">
+        <f>[19]Overview!$C$25</f>
+        <v>326.28571428571428</v>
+      </c>
+      <c r="J21" s="14">
+        <f>[19]Overview!$C$21</f>
+        <v>-2.2857142857142856</v>
+      </c>
+      <c r="K21" s="13">
+        <f>[19]Overview!$F$24</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="L21" s="14">
+        <f>[19]Overview!$F$25</f>
+        <v>142.76923076923077</v>
+      </c>
+      <c r="M21" s="15">
+        <f>[19]Overview!$F$21</f>
+        <v>0.23076923076923078</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="26">
         <f>AVERAGE(SLAs_Over_Time[On Time 1])</f>
-        <v>0.57466931216931227</v>
-      </c>
-      <c r="C21" s="22">
+        <v>0.57951127819548875</v>
+      </c>
+      <c r="C22" s="22">
         <f>AVERAGE(SLAs_Over_Time[Average Billed Minutes 1])</f>
-        <v>127.02323633156968</v>
-      </c>
-      <c r="D21" s="22">
+        <v>126.96938178780286</v>
+      </c>
+      <c r="D22" s="22">
         <f>AVERAGE(SLAs_Over_Time[Average Days Overdue 1])</f>
-        <v>1.3474206349206348</v>
-      </c>
-      <c r="E21" s="26">
+        <v>1.250187969924812</v>
+      </c>
+      <c r="E22" s="26">
         <f>AVERAGE(SLAs_Over_Time[On Time 2])</f>
-        <v>0.78428571428571425</v>
-      </c>
-      <c r="F21" s="22">
+        <v>0.79776785714285714</v>
+      </c>
+      <c r="F22" s="22">
         <f>AVERAGE(SLAs_Over_Time[Average Billed Minutes 2])</f>
-        <v>38.441904761904759</v>
-      </c>
-      <c r="G21" s="23">
+        <v>38.039285714285711</v>
+      </c>
+      <c r="G22" s="23">
         <f>AVERAGE(SLAs_Over_Time[Average Days Overdue 2])</f>
-        <v>-1.886190476190476</v>
-      </c>
-      <c r="H21" s="26">
+        <v>-1.9870535714285713</v>
+      </c>
+      <c r="H22" s="26">
         <f>AVERAGE(SLAs_Over_Time[On Time 3])</f>
-        <v>0.2287437870771204</v>
-      </c>
-      <c r="I21" s="22">
+        <v>0.27664616085668714</v>
+      </c>
+      <c r="I22" s="22">
         <f>AVERAGE(SLAs_Over_Time[Average Billed Minutes 3])</f>
-        <v>526.3869508577842</v>
-      </c>
-      <c r="J21" s="22">
+        <v>515.88016062884481</v>
+      </c>
+      <c r="J22" s="22">
         <f>AVERAGE(SLAs_Over_Time[Average Days Overdue 3])</f>
-        <v>20.63477032227032</v>
-      </c>
-      <c r="K21" s="26">
+        <v>19.374335459861776</v>
+      </c>
+      <c r="K22" s="26">
         <f>AVERAGE(SLAs_Over_Time[On Time 4])</f>
-        <v>0.32426470588235295</v>
-      </c>
-      <c r="L21" s="22">
+        <v>0.37370537958773253</v>
+      </c>
+      <c r="L22" s="22">
         <f>AVERAGE(SLAs_Over_Time[Average Billed Minutes 4])</f>
-        <v>170.14434523809524</v>
-      </c>
-      <c r="M21" s="23">
+        <v>170.54711029711029</v>
+      </c>
+      <c r="M22" s="23">
         <f>AVERAGE(SLAs_Over_Time[Average Days Overdue 4])</f>
-        <v>17.596376050420169</v>
+        <v>15.666864181570064</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="20" t="s">
+    <row r="23" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B23" s="27">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[On Time 1], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>0.51177248677248666</v>
-      </c>
-      <c r="C22" s="17">
+        <v>0.52726190476190471</v>
+      </c>
+      <c r="C23" s="17">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Billed Minutes 1], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>141.57354497354495</v>
-      </c>
-      <c r="D22" s="18">
+        <v>140.01619047619047</v>
+      </c>
+      <c r="D23" s="18">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Days Overdue 1], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>2.5649470899470899</v>
-      </c>
-      <c r="E22" s="27">
+        <v>2.2584523809523809</v>
+      </c>
+      <c r="E23" s="27">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[On Time 2], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>0.58571428571428574</v>
-      </c>
-      <c r="F22" s="17">
+        <v>0.64489795918367343</v>
+      </c>
+      <c r="F23" s="17">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Billed Minutes 2], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>60.354761904761908</v>
-      </c>
-      <c r="G22" s="18">
+        <v>56.304081632653059</v>
+      </c>
+      <c r="G23" s="18">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Days Overdue 2], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>0.24285714285714288</v>
-      </c>
-      <c r="H22" s="27">
+        <v>-0.29183673469387755</v>
+      </c>
+      <c r="H23" s="27">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[On Time 3], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>0.37331248997915661</v>
-      </c>
-      <c r="I22" s="17">
+        <v>0.44987012987012986</v>
+      </c>
+      <c r="I23" s="17">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Billed Minutes 3], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>336.72673961840633</v>
-      </c>
-      <c r="J22" s="18">
+        <v>335.72985930735933</v>
+      </c>
+      <c r="J23" s="18">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Days Overdue 3], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>9.4048460798460773</v>
-      </c>
-      <c r="K22" s="27">
+        <v>8.1330122655122636</v>
+      </c>
+      <c r="K23" s="27">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[On Time 4], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>0.32426470588235295</v>
-      </c>
-      <c r="L22" s="17">
+        <v>0.37370537958773253</v>
+      </c>
+      <c r="L23" s="17">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Billed Minutes 4], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>170.14434523809524</v>
-      </c>
-      <c r="M22" s="18">
+        <v>170.54711029711029</v>
+      </c>
+      <c r="M23" s="18">
         <f ca="1">AVERAGEIFS(SLAs_Over_Time[Average Days Overdue 4], SLAs_Over_Time[Month], "&gt;=1/1/" &amp; YEAR(TODAY()), SLAs_Over_Time[Month], "&lt;=12/31/" &amp; YEAR(TODAY()))</f>
-        <v>17.596376050420169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="K23" s="5"/>
+        <v>15.666864181570064</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
@@ -15320,21 +15516,18 @@
       <c r="E42" s="5"/>
       <c r="K42" s="5"/>
     </row>
-    <row r="58" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="K43" s="5"/>
     </row>
     <row r="59" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F59" s="5"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
     </row>
     <row r="60" spans="6:11" x14ac:dyDescent="0.3">
       <c r="F60" s="5"/>
@@ -15481,10 +15674,10 @@
       <c r="K77" s="4"/>
     </row>
     <row r="78" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F78" s="10"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
-      <c r="I78" s="10"/>
+      <c r="I78" s="5"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
     </row>
@@ -15495,6 +15688,14 @@
       <c r="I79" s="10"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
+    </row>
+    <row r="80" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F80" s="10"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="10"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
